--- a/templates/Strukturvorlage_DataDictionary_Aargau_iDSK_SelectedClasses_v0.1.0.xlsx
+++ b/templates/Strukturvorlage_DataDictionary_Aargau_iDSK_SelectedClasses_v0.1.0.xlsx
@@ -2445,7 +2445,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="49.28515625" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
-    <col width="1.7109375" customWidth="1" style="35" min="2" max="2"/>
+    <col width="28" customWidth="1" style="35" min="2" max="2"/>
     <col width="12.5703125" customWidth="1" style="77" min="3" max="3"/>
     <col width="1.7109375" customWidth="1" style="35" min="4" max="4"/>
     <col width="8.140625" bestFit="1" customWidth="1" style="77" min="5" max="5"/>
@@ -2469,6 +2469,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.65" customHeight="1" s="227">
+      <c r="B1" s="34" t="inlineStr">
+        <is>
+          <t>Data Templates</t>
+        </is>
+      </c>
       <c r="C1" s="34" t="inlineStr">
         <is>
           <t>GoP</t>
@@ -2616,6 +2621,11 @@
       <c r="EA1" s="231" t="n"/>
     </row>
     <row r="2" ht="163.5" customFormat="1" customHeight="1" s="159">
+      <c r="B2" s="76" t="inlineStr">
+        <is>
+          <t>DataTemplate-ID</t>
+        </is>
+      </c>
       <c r="C2" s="76" t="inlineStr">
         <is>
           <t>GoP - Designation/Bezeichnung/Désignation/Designazione</t>
@@ -2980,7 +2990,11 @@
           <t>Classes</t>
         </is>
       </c>
-      <c r="B3" s="75" t="n"/>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Stable identity</t>
+        </is>
+      </c>
       <c r="D3" s="75" t="n"/>
       <c r="F3" s="78" t="n"/>
       <c r="G3" s="78" t="n"/>
@@ -3042,7 +3056,11 @@
           <t>Class - Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
-      <c r="B4" s="171" t="n"/>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Repeat the same ID across rows to attach 0..n GroupOfProperties</t>
+        </is>
+      </c>
       <c r="C4" s="172" t="n"/>
       <c r="D4" s="171" t="n"/>
       <c r="E4" s="172" t="n"/>
@@ -3108,7 +3126,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B5" s="75" t="n"/>
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>0005-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C5" s="81" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -3264,7 +3286,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B6" s="75" t="n"/>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>0006-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C6" s="81" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -3420,7 +3446,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B7" s="84" t="n"/>
+      <c r="B7" s="84" t="inlineStr">
+        <is>
+          <t>0007-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -3576,7 +3606,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B8" s="84" t="n"/>
+      <c r="B8" s="84" t="inlineStr">
+        <is>
+          <t>0008-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -3732,7 +3766,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B9" s="84" t="n"/>
+      <c r="B9" s="84" t="inlineStr">
+        <is>
+          <t>0009-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -3888,7 +3926,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B10" s="84" t="n"/>
+      <c r="B10" s="84" t="inlineStr">
+        <is>
+          <t>0010-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C10" s="40" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -4044,7 +4086,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B11" s="84" t="n"/>
+      <c r="B11" s="84" t="inlineStr">
+        <is>
+          <t>0011-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -4200,7 +4246,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B12" s="84" t="n"/>
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>0012-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C12" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -4356,7 +4406,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B13" s="84" t="n"/>
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>0013-ramp-agatb-atb-rds</t>
+        </is>
+      </c>
       <c r="C13" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_RDS</t>
@@ -4512,7 +4566,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B14" s="84" t="n"/>
+      <c r="B14" s="84" t="inlineStr">
+        <is>
+          <t>0014-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C14" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -4680,7 +4738,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B15" s="84" t="n"/>
+      <c r="B15" s="84" t="inlineStr">
+        <is>
+          <t>0015-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C15" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -4848,7 +4910,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B16" s="84" t="n"/>
+      <c r="B16" s="84" t="inlineStr">
+        <is>
+          <t>0016-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C16" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -5016,7 +5082,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B17" s="84" t="n"/>
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>0017-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C17" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -5184,7 +5254,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B18" s="84" t="n"/>
+      <c r="B18" s="84" t="inlineStr">
+        <is>
+          <t>0018-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C18" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -5352,7 +5426,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B19" s="84" t="n"/>
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>0019-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C19" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -5520,7 +5598,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B20" s="84" t="n"/>
+      <c r="B20" s="84" t="inlineStr">
+        <is>
+          <t>0020-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C20" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -5688,7 +5770,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B21" s="84" t="n"/>
+      <c r="B21" s="84" t="inlineStr">
+        <is>
+          <t>0021-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C21" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -5856,7 +5942,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B22" s="84" t="n"/>
+      <c r="B22" s="84" t="inlineStr">
+        <is>
+          <t>0022-ramp-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C22" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -6024,7 +6114,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B23" s="84" t="n"/>
+      <c r="B23" s="84" t="inlineStr">
+        <is>
+          <t>0023-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C23" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -6196,7 +6290,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B24" s="84" t="n"/>
+      <c r="B24" s="84" t="inlineStr">
+        <is>
+          <t>0024-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C24" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -6368,7 +6466,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B25" s="84" t="n"/>
+      <c r="B25" s="84" t="inlineStr">
+        <is>
+          <t>0025-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C25" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -6540,7 +6642,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B26" s="84" t="n"/>
+      <c r="B26" s="84" t="inlineStr">
+        <is>
+          <t>0026-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C26" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -6712,7 +6818,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B27" s="84" t="n"/>
+      <c r="B27" s="84" t="inlineStr">
+        <is>
+          <t>0027-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C27" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -6884,7 +6994,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B28" s="84" t="n"/>
+      <c r="B28" s="84" t="inlineStr">
+        <is>
+          <t>0028-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C28" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -7056,7 +7170,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B29" s="84" t="n"/>
+      <c r="B29" s="84" t="inlineStr">
+        <is>
+          <t>0029-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C29" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -7228,7 +7346,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B30" s="84" t="n"/>
+      <c r="B30" s="84" t="inlineStr">
+        <is>
+          <t>0030-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C30" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -7400,7 +7522,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B31" s="84" t="n"/>
+      <c r="B31" s="84" t="inlineStr">
+        <is>
+          <t>0031-ramp-agatb-atb-lifecycle</t>
+        </is>
+      </c>
       <c r="C31" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Lifecycle</t>
@@ -7572,7 +7698,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B32" s="84" t="n"/>
+      <c r="B32" s="84" t="inlineStr">
+        <is>
+          <t>0032-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C32" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -7728,7 +7858,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B33" s="84" t="n"/>
+      <c r="B33" s="84" t="inlineStr">
+        <is>
+          <t>0033-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C33" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -7884,7 +8018,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B34" s="84" t="n"/>
+      <c r="B34" s="84" t="inlineStr">
+        <is>
+          <t>0034-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C34" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8040,7 +8178,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B35" s="84" t="n"/>
+      <c r="B35" s="84" t="inlineStr">
+        <is>
+          <t>0035-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C35" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8196,7 +8338,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B36" s="84" t="n"/>
+      <c r="B36" s="84" t="inlineStr">
+        <is>
+          <t>0036-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C36" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8352,7 +8498,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B37" s="84" t="n"/>
+      <c r="B37" s="84" t="inlineStr">
+        <is>
+          <t>0037-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C37" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8508,7 +8658,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B38" s="84" t="n"/>
+      <c r="B38" s="84" t="inlineStr">
+        <is>
+          <t>0038-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C38" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8664,7 +8818,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B39" s="84" t="n"/>
+      <c r="B39" s="84" t="inlineStr">
+        <is>
+          <t>0039-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C39" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8820,7 +8978,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B40" s="84" t="n"/>
+      <c r="B40" s="84" t="inlineStr">
+        <is>
+          <t>0040-ramp-agatb-atb-lifecyclestatus</t>
+        </is>
+      </c>
       <c r="C40" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_LifecycleStatus</t>
@@ -8976,7 +9138,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B41" s="84" t="n"/>
+      <c r="B41" s="84" t="inlineStr">
+        <is>
+          <t>0041-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C41" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -9132,7 +9298,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B42" s="84" t="n"/>
+      <c r="B42" s="84" t="inlineStr">
+        <is>
+          <t>0042-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C42" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -9288,7 +9458,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B43" s="84" t="n"/>
+      <c r="B43" s="84" t="inlineStr">
+        <is>
+          <t>0043-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C43" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -9444,7 +9618,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B44" s="84" t="n"/>
+      <c r="B44" s="84" t="inlineStr">
+        <is>
+          <t>0044-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C44" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -9600,7 +9778,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B45" s="84" t="n"/>
+      <c r="B45" s="84" t="inlineStr">
+        <is>
+          <t>0045-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C45" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -9756,7 +9938,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B46" s="84" t="n"/>
+      <c r="B46" s="84" t="inlineStr">
+        <is>
+          <t>0046-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C46" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -9912,7 +10098,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B47" s="84" t="n"/>
+      <c r="B47" s="84" t="inlineStr">
+        <is>
+          <t>0047-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C47" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -10068,7 +10258,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B48" s="84" t="n"/>
+      <c r="B48" s="84" t="inlineStr">
+        <is>
+          <t>0048-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C48" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -10224,7 +10418,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B49" s="84" t="n"/>
+      <c r="B49" s="84" t="inlineStr">
+        <is>
+          <t>0049-ramp-agatb-ifc-material</t>
+        </is>
+      </c>
       <c r="C49" s="86" t="inlineStr">
         <is>
           <t>agatb_IFC_Material</t>
@@ -10380,7 +10578,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B50" s="84" t="n"/>
+      <c r="B50" s="84" t="inlineStr">
+        <is>
+          <t>0050-ramp-agatb-kb-infkuba-bauteil</t>
+        </is>
+      </c>
       <c r="C50" s="86" t="inlineStr">
         <is>
           <t>agatb_KB_infKuba_Bauteil</t>
@@ -10564,7 +10766,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B51" s="84" t="n"/>
+      <c r="B51" s="84" t="inlineStr">
+        <is>
+          <t>0051-ramp-agatb-kb-infkuba-bauteil</t>
+        </is>
+      </c>
       <c r="C51" s="86" t="inlineStr">
         <is>
           <t>agatb_KB_infKuba_Bauteil</t>
@@ -10748,7 +10954,11 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="B52" s="84" t="n"/>
+      <c r="B52" s="84" t="inlineStr">
+        <is>
+          <t>0052-ramp-agatb-kb-infkuba-bauteil</t>
+        </is>
+      </c>
       <c r="C52" s="86" t="inlineStr">
         <is>
           <t>agatb_KB_infKuba_Bauteil</t>
@@ -10932,7 +11142,11 @@
           <t>Bridge</t>
         </is>
       </c>
-      <c r="B53" s="84" t="n"/>
+      <c r="B53" s="84" t="inlineStr">
+        <is>
+          <t>0053-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C53" s="86" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11100,6 +11314,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0054-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C54" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11155,6 +11374,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0055-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C55" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11210,6 +11434,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0056-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C56" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11265,6 +11494,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0057-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C57" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11320,6 +11554,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0058-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C58" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11375,6 +11614,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0059-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C59" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11430,6 +11674,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0060-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C60" s="87" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11485,6 +11734,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0061-bridge-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11537,6 +11791,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0062-bridge-agatb-kb-infkuba-bauwerk</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>agatb_KB_infKuba_Bauwerk</t>
@@ -11609,6 +11868,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0063-bridge-agatb-kb-infkuba-bauwerk</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>agatb_KB_infKuba_Bauwerk</t>
@@ -11681,6 +11945,11 @@
           <t>Bridge</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0064-bridge-agatb-kb-infkuba-bauwerk</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>agatb_KB_infKuba_Bauwerk</t>
@@ -11753,6 +12022,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0065-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11805,6 +12079,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0066-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11857,6 +12136,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0067-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11909,6 +12193,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0068-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -11961,6 +12250,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0069-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12013,6 +12307,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0070-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12065,6 +12364,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0071-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12117,6 +12421,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0072-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12169,6 +12478,11 @@
           <t>Building</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0073-building-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12221,6 +12535,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0074-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12273,6 +12592,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0075-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12325,6 +12649,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0076-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12377,6 +12706,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0077-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12429,6 +12763,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0078-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12481,6 +12820,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0079-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12533,6 +12877,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0080-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12585,6 +12934,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0081-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12637,6 +12991,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0082-carriageway-bus-stop-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -12689,6 +13048,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0083-carriageway-bus-stop-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -12746,6 +13110,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0084-carriageway-bus-stop-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -12803,6 +13172,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0085-carriageway-bus-stop-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -12860,6 +13234,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0086-carriageway-bus-stop-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -12927,6 +13306,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0087-carriageway-bus-stop-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -12994,6 +13378,11 @@
           <t>Carriageway bus stop</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0088-carriageway-bus-stop-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -13061,6 +13450,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0089-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13113,6 +13507,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0090-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13165,6 +13564,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0091-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13217,6 +13621,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0092-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13269,6 +13678,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0093-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13321,6 +13735,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0094-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13373,6 +13792,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0095-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13425,6 +13849,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0096-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13477,6 +13906,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0097-roundabout-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -13529,6 +13963,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0098-roundabout-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -13586,6 +14025,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0099-roundabout-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -13643,6 +14087,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0100-roundabout-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -13700,6 +14149,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0101-roundabout-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -13767,6 +14221,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0102-roundabout-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -13834,6 +14293,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0103-roundabout-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -13901,6 +14365,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0104-roundabout-agatb-tras-geometrie-strassenraum</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
           <t>agatb_TRAS_Geometrie_Strassenraum</t>
@@ -13968,6 +14437,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0105-roundabout-agatb-tras-geometrie-strassenraum</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>agatb_TRAS_Geometrie_Strassenraum</t>
@@ -14035,6 +14509,11 @@
           <t>Roundabout</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0106-roundabout-agatb-tras-geometrie-strassenraum</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
           <t>agatb_TRAS_Geometrie_Strassenraum</t>
@@ -14102,6 +14581,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0107-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14154,6 +14638,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0108-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14206,6 +14695,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0109-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14258,6 +14752,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0110-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14310,6 +14809,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0111-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14362,6 +14866,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0112-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14414,6 +14923,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0113-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14466,6 +14980,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0114-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14518,6 +15037,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0115-road-segment-agatb-atb-informierung</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>agatb_ATB_Informierung</t>
@@ -14570,6 +15094,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0116-road-segment-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -14627,6 +15156,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0117-road-segment-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -14684,6 +15218,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0118-road-segment-agatb-tras-identifikation</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
           <t>agatb_TRAS_Identifikation</t>
@@ -14741,6 +15280,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0119-road-segment-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -14808,6 +15352,11 @@
           <t>Road segment</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0120-road-segment-agatb-tras-achsreferenz</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr">
         <is>
           <t>agatb_TRAS_Achsreferenz</t>
@@ -14873,6 +15422,11 @@
       <c r="A121" t="inlineStr">
         <is>
           <t>Road segment</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0121-road-segment-agatb-tras-achsreferenz</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
